--- a/Line Item Charges grant/charges.xlsx
+++ b/Line Item Charges grant/charges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mike\Documents\GitHub\Flexi-TEER\Line Item Charges grant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F143AF0-8D77-4F4D-9271-7A5E544EEA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8138B68E-98E3-4B4E-AB89-02EC52C1E046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6E327D4-087E-436A-9325-800F9F705EE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20856" windowHeight="16776" xr2:uid="{D6E327D4-087E-436A-9325-800F9F705EE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Purchase</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>solder</t>
+  </si>
+  <si>
+    <t>amazon order 4</t>
+  </si>
+  <si>
+    <t>wash bucket for SLA washing station</t>
   </si>
 </sst>
 </file>
@@ -492,16 +498,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BDFD9D3-524C-422C-ABD1-C3247FE6B603}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,7 +521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -527,10 +533,10 @@
       </c>
       <c r="G3">
         <f>SUM(C3:C27)</f>
-        <v>3075.27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3107.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -541,7 +547,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -552,7 +558,7 @@
         <v>13.84</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -563,7 +569,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -571,7 +577,7 @@
         <v>279.61</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -582,7 +588,7 @@
         <v>88.18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -593,7 +599,7 @@
         <v>1557.64</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -604,7 +610,7 @@
         <v>272.54000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -615,7 +621,7 @@
         <v>256.60000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -626,7 +632,7 @@
         <v>127.06</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -637,7 +643,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -648,7 +654,7 @@
         <v>69.42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -659,7 +665,7 @@
         <v>252.52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -670,7 +676,7 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -679,6 +685,17 @@
       </c>
       <c r="C17">
         <v>12.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>32.090000000000003</v>
       </c>
     </row>
   </sheetData>
